--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,6 +1258,788 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125384920</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>793391</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7255000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125385267</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>793391</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7255000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125389609</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>793429</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7254854</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På död stående gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125389359</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>793371</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7254870</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125390233</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>793530</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7254884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125390957</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>793641</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7255376</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stort antal plantor i detta område.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125389924</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>793454</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7254838</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På stubbe och låga av gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2040,6 +2040,113 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125385144</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91210</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>793554</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7254928</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125384920</v>
+        <v>125390957</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,46 +1272,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>793391</v>
+        <v>793641</v>
       </c>
       <c r="R7" t="n">
-        <v>7255000</v>
+        <v>7255376</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,6 +1346,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125385267</v>
+        <v>125384920</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,43 +1389,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Område kring bäck, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1463,7 +1466,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1594,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125389359</v>
+        <v>125390233</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,43 +1608,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>793371</v>
+        <v>793530</v>
       </c>
       <c r="R10" t="n">
-        <v>7254870</v>
+        <v>7254884</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1675,11 +1677,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125390233</v>
+        <v>125385267</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1745,16 +1742,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>793530</v>
+        <v>793391</v>
       </c>
       <c r="R11" t="n">
-        <v>7254884</v>
+        <v>7255000</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1795,6 +1799,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1813,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125390957</v>
+        <v>125389924</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,51 +1830,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>793641</v>
+        <v>793454</v>
       </c>
       <c r="R12" t="n">
-        <v>7255376</v>
+        <v>7254838</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stort antal plantor i detta område.</t>
+          <t>På stubbe och låga av gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125389924</v>
+        <v>125389359</v>
       </c>
       <c r="B13" t="n">
         <v>91030</v>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>793454</v>
+        <v>793371</v>
       </c>
       <c r="R13" t="n">
-        <v>7254838</v>
+        <v>7254870</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På stubbe och låga av gran.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125390957</v>
+        <v>125390233</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,24 +1299,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>793641</v>
+        <v>793530</v>
       </c>
       <c r="R7" t="n">
-        <v>7255376</v>
+        <v>7254884</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,11 +1341,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125384920</v>
+        <v>125389609</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91162</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,27 +1383,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>793391</v>
+        <v>793429</v>
       </c>
       <c r="R8" t="n">
-        <v>7255000</v>
+        <v>7254854</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1458,6 +1448,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På död stående gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125389609</v>
+        <v>125389359</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>793429</v>
+        <v>793371</v>
       </c>
       <c r="R9" t="n">
-        <v>7254854</v>
+        <v>7254870</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död stående gran.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125390233</v>
+        <v>125385267</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,16 +1630,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>793530</v>
+        <v>793391</v>
       </c>
       <c r="R10" t="n">
-        <v>7254884</v>
+        <v>7255000</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1685,6 +1687,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125385267</v>
+        <v>125384920</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,43 +1718,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Område kring bäck, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1799,7 +1795,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1821,7 +1816,7 @@
         <v>125389924</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1930,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125389359</v>
+        <v>125390957</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,46 +1937,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>793371</v>
+        <v>793641</v>
       </c>
       <c r="R13" t="n">
-        <v>7254870</v>
+        <v>7255376</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,7 +2045,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91210</v>
+        <v>91364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125390233</v>
+        <v>125385267</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
@@ -1299,16 +1299,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>793530</v>
+        <v>793391</v>
       </c>
       <c r="R7" t="n">
-        <v>7254884</v>
+        <v>7255000</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1349,6 +1356,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125389609</v>
+        <v>125384920</v>
       </c>
       <c r="B8" t="n">
-        <v>91162</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,27 +1391,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>793429</v>
+        <v>793391</v>
       </c>
       <c r="R8" t="n">
-        <v>7254854</v>
+        <v>7255000</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1448,11 +1456,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På död stående gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125389359</v>
+        <v>125390957</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,46 +1494,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>793371</v>
+        <v>793641</v>
       </c>
       <c r="R9" t="n">
-        <v>7254870</v>
+        <v>7255376</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1572,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1599,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125385267</v>
+        <v>125390233</v>
       </c>
       <c r="B10" t="n">
         <v>98269</v>
@@ -1630,23 +1638,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>793391</v>
+        <v>793530</v>
       </c>
       <c r="R10" t="n">
-        <v>7255000</v>
+        <v>7254884</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1687,7 +1688,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125384920</v>
+        <v>125389609</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>91162</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,27 +1722,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>793391</v>
+        <v>793429</v>
       </c>
       <c r="R11" t="n">
-        <v>7255000</v>
+        <v>7254854</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1787,6 +1787,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På död stående gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125389924</v>
+        <v>125389359</v>
       </c>
       <c r="B12" t="n">
         <v>91184</v>
@@ -1858,13 +1863,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>793454</v>
+        <v>793371</v>
       </c>
       <c r="R12" t="n">
-        <v>7254838</v>
+        <v>7254870</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,7 +1903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På stubbe och låga av gran.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125390957</v>
+        <v>125389924</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>91184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,51 +1942,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>793641</v>
+        <v>793454</v>
       </c>
       <c r="R13" t="n">
-        <v>7255376</v>
+        <v>7254838</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stort antal plantor i detta område.</t>
+          <t>På stubbe och låga av gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1260,65 +1260,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125385267</v>
+        <v>125389924</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Område kring bäck, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>793391</v>
+        <v>793454</v>
       </c>
       <c r="R7" t="n">
-        <v>7255000</v>
+        <v>7254838</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,13 +1338,17 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På stubbe och låga av gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,15 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125384920</v>
+        <v>125389359</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,27 +1378,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>793391</v>
+        <v>793371</v>
       </c>
       <c r="R8" t="n">
-        <v>7255000</v>
+        <v>7254870</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1456,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125390957</v>
+        <v>125390233</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,24 +1508,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>793641</v>
+        <v>793530</v>
       </c>
       <c r="R9" t="n">
-        <v>7255376</v>
+        <v>7254884</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,11 +1550,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,15 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125390233</v>
+        <v>125390957</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,19 +1610,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>793530</v>
+        <v>793641</v>
       </c>
       <c r="R10" t="n">
-        <v>7254884</v>
+        <v>7255376</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,6 +1657,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,12 +1691,7 @@
         <v>125389609</v>
       </c>
       <c r="B11" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,15 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125389359</v>
+        <v>125384920</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,27 +1806,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1863,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>793371</v>
+        <v>793391</v>
       </c>
       <c r="R12" t="n">
-        <v>7254870</v>
+        <v>7255000</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1899,11 +1871,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,58 +1897,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125389924</v>
+        <v>125385267</v>
       </c>
       <c r="B13" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>793454</v>
+        <v>793391</v>
       </c>
       <c r="R13" t="n">
-        <v>7254838</v>
+        <v>7255000</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,17 +1982,13 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På stubbe och låga av gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2045,12 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91364</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,6 +2041,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Område kring bäck, Område kring bäck, Nb</t>
@@ -2131,6 +2093,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>125389924</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>125389359</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>125390233</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>125390957</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>125389609</v>
       </c>
       <c r="B11" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>125385267</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91418</v>
+        <v>91425</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91425</v>
+        <v>91426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>125389924</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>125389359</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>125390233</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>125390957</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>125389609</v>
       </c>
       <c r="B11" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>125385267</v>
       </c>
       <c r="B13" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91426</v>
+        <v>91429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>125389924</v>
       </c>
       <c r="B7" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>125389359</v>
       </c>
       <c r="B8" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>125390233</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>125390957</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>125389609</v>
       </c>
       <c r="B11" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>125385267</v>
       </c>
       <c r="B13" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91429</v>
+        <v>91433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -1477,7 +1477,7 @@
         <v>125390233</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>125390957</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>125385267</v>
       </c>
       <c r="B13" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91433</v>
+        <v>91435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91435</v>
+        <v>91437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91437</v>
+        <v>91439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,6 +2109,108 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126264373</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>793388</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7254915</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91439</v>
+        <v>91443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>126264373</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91443</v>
+        <v>91446</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>126264373</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2212,6 +2212,113 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128751800</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>793414</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7255053</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack i murken tallåga.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>128751800</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>128751800</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>128751800</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>128751800</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2217,7 +2217,7 @@
         <v>128751800</v>
       </c>
       <c r="B16" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>91446</v>
+        <v>92132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
@@ -2319,6 +2319,346 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133760504</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Område vid bäck, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>793529</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7254875</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>11 ägg i bo. Stötte upp ruvande fågeln mindre än en meter ifrån den.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133736433</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>793556</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7254887</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133735545</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>793616</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7254868</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2321,64 +2321,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133760504</v>
+        <v>133736433</v>
       </c>
       <c r="B17" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Område vid bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>793529</v>
+        <v>793556</v>
       </c>
       <c r="R17" t="n">
-        <v>7254875</v>
+        <v>7254887</v>
       </c>
       <c r="S17" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,11 +2406,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>11 ägg i bo. Stötte upp ruvande fågeln mindre än en meter ifrån den.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,7 +2432,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133736433</v>
+        <v>133735545</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2469,7 +2462,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2488,13 +2481,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>793556</v>
+        <v>793616</v>
       </c>
       <c r="R18" t="n">
-        <v>7254887</v>
+        <v>7254868</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2550,62 +2543,64 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133735545</v>
+        <v>133760504</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Område vid bäck, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>793616</v>
+        <v>793529</v>
       </c>
       <c r="R19" t="n">
-        <v>7254868</v>
+        <v>7254875</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,6 +2630,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nio ägg i bo. Stötte upp ruvande fågeln mindre än en meter ifrån den.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,6 +2658,108 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133734099</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>793774</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7254934</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>133736433</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>133735545</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>92134</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>133736433</v>
       </c>
       <c r="B17" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>133735545</v>
       </c>
       <c r="B18" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>133736433</v>
       </c>
       <c r="B17" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>133735545</v>
       </c>
       <c r="B18" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -2010,7 +2010,7 @@
         <v>125385144</v>
       </c>
       <c r="B14" t="n">
-        <v>92579</v>
+        <v>92586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>133736433</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>133735545</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117098826</v>
+        <v>125385144</v>
       </c>
       <c r="B2" t="n">
-        <v>56486</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>793672</v>
+        <v>793554</v>
       </c>
       <c r="R2" t="n">
-        <v>7254965</v>
+        <v>7254928</v>
       </c>
       <c r="S2" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,25 +747,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I anslutning till bäckarna.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,65 +780,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117098806</v>
+        <v>125389609</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793672</v>
+        <v>793429</v>
       </c>
       <c r="R3" t="n">
-        <v>7254965</v>
+        <v>7254854</v>
       </c>
       <c r="S3" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död stående gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,69 +887,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118967850</v>
+        <v>125384920</v>
       </c>
       <c r="B4" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>793540</v>
+        <v>793391</v>
       </c>
       <c r="R4" t="n">
-        <v>7254866</v>
+        <v>7255000</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +971,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,69 +989,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118967122</v>
+        <v>128751800</v>
       </c>
       <c r="B5" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793550</v>
+        <v>793414</v>
       </c>
       <c r="R5" t="n">
-        <v>7254890</v>
+        <v>7255053</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,12 +1059,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i murken tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119113375</v>
+        <v>126264373</v>
       </c>
       <c r="B6" t="n">
-        <v>58195</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,49 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
+          <t>Område kring bäck, Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>793672</v>
+        <v>793388</v>
       </c>
       <c r="R6" t="n">
-        <v>7254965</v>
+        <v>7254915</v>
       </c>
       <c r="S6" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,12 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125389924</v>
+        <v>133734099</v>
       </c>
       <c r="B7" t="n">
-        <v>91250</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,42 +1209,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>793454</v>
+        <v>793774</v>
       </c>
       <c r="R7" t="n">
-        <v>7254838</v>
+        <v>7254934</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,17 +1268,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På stubbe och låga av gran.</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,53 +1300,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125389359</v>
+        <v>117098826</v>
       </c>
       <c r="B8" t="n">
-        <v>91250</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>793371</v>
+        <v>793672</v>
       </c>
       <c r="R8" t="n">
-        <v>7254870</v>
+        <v>7254965</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,17 +1377,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>I anslutning till bäckarna.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,53 +1414,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125390233</v>
+        <v>117098806</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>793530</v>
+        <v>793672</v>
       </c>
       <c r="R9" t="n">
-        <v>7254884</v>
+        <v>7254965</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,58 +1523,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125390957</v>
+        <v>134262512</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
+          <t>Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>793641</v>
+        <v>793594</v>
       </c>
       <c r="R10" t="n">
-        <v>7255376</v>
+        <v>7255369</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,17 +1600,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stort antal plantor i detta område.</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,38 +1632,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125389609</v>
+        <v>133737436</v>
       </c>
       <c r="B11" t="n">
-        <v>91228</v>
+        <v>58131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1728,13 +1676,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>793429</v>
+        <v>793519</v>
       </c>
       <c r="R11" t="n">
-        <v>7254854</v>
+        <v>7254862</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,17 +1706,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död stående gran.</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,53 +1738,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125384920</v>
+        <v>119113375</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>58656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103056</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>793391</v>
+        <v>793672</v>
       </c>
       <c r="R12" t="n">
-        <v>7255000</v>
+        <v>7254965</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,12 +1815,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125385267</v>
+        <v>118967122</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1875,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1933,24 +1887,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>793391</v>
+        <v>793550</v>
       </c>
       <c r="R13" t="n">
-        <v>7255000</v>
+        <v>7254890</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,12 +1928,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125385144</v>
+        <v>118967850</v>
       </c>
       <c r="B14" t="n">
-        <v>92586</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,44 +1972,53 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>793554</v>
+        <v>793540</v>
       </c>
       <c r="R14" t="n">
-        <v>7254928</v>
+        <v>7254866</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2079,19 +2042,19 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
@@ -2112,53 +2075,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126264373</v>
+        <v>125385267</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Område kring bäck, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>793388</v>
+        <v>793391</v>
       </c>
       <c r="R15" t="n">
-        <v>7254915</v>
+        <v>7255000</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2182,12 +2152,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,6 +2166,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2214,53 +2185,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128751800</v>
+        <v>125390233</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Område kring bäck, Område kring bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>793414</v>
+        <v>793530</v>
       </c>
       <c r="R16" t="n">
-        <v>7255053</v>
+        <v>7254884</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2284,17 +2255,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack i murken tallåga.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133736433</v>
+        <v>125390957</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,14 +2315,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2366,17 +2328,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
+          <t>Skog SV Råmyrberget, Skog SV Råmyrberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>793556</v>
+        <v>793641</v>
       </c>
       <c r="R17" t="n">
-        <v>7254887</v>
+        <v>7255376</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2400,12 +2362,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Stort antal plantor i detta område.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,7 +2402,7 @@
         <v>133735545</v>
       </c>
       <c r="B18" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,64 +2510,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133760504</v>
+        <v>133736433</v>
       </c>
       <c r="B19" t="n">
-        <v>57153</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Område vid bäck, Nb</t>
+          <t>Gammal skog SV Råmyran, Gammal skog SV Råmyran, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>793529</v>
+        <v>793556</v>
       </c>
       <c r="R19" t="n">
-        <v>7254875</v>
+        <v>7254887</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2630,11 +2595,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Nio ägg i bo. Stötte upp ruvande fågeln mindre än en meter ifrån den.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,217 +2618,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>133734099</v>
-      </c>
-      <c r="B20" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Gammal skog SV Råmyran, Bergsviken, Nb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>793774</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7254934</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Piteå socken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Tomas Carlsson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Tomas Carlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>134262512</v>
-      </c>
-      <c r="B21" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Skog SV Råmyrberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>793594</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7255369</v>
-      </c>
-      <c r="S21" t="n">
-        <v>75</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Piteå socken</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Tomas Carlsson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Tomas Carlsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20961-2025 artfynd.xlsx
+++ b/artfynd/A 20961-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125385144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125389609</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125384920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128751800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126264373</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133734099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117098826</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117098806</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,6 +1785,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737436</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119113375</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967850</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2182,6 +2252,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125385267</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2284,6 +2359,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125390233</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125390957</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133735545</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,8 +2708,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133736433</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>